--- a/output/tables/table_S3_healthy_days_2.0.xlsx
+++ b/output/tables/table_S3_healthy_days_2.0.xlsx
@@ -1025,7 +1025,16 @@
         <v>106</v>
       </c>
       <c r="I16" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>97.17</v>
+      </c>
+      <c r="K16">
+        <v>84.91</v>
+      </c>
+      <c r="L16">
+        <v>23.58</v>
       </c>
     </row>
     <row r="17">
@@ -1142,7 +1151,16 @@
         <v>106</v>
       </c>
       <c r="I19" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>80.19</v>
+      </c>
+      <c r="K19">
+        <v>54.72</v>
+      </c>
+      <c r="L19">
+        <v>15.09</v>
       </c>
     </row>
     <row r="20">
@@ -1259,7 +1277,16 @@
         <v>106</v>
       </c>
       <c r="I22" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>58.49</v>
+      </c>
+      <c r="K22">
+        <v>36.79</v>
+      </c>
+      <c r="L22">
+        <v>10.38</v>
       </c>
     </row>
     <row r="23">

--- a/output/tables/table_S3_healthy_days_2.0.xlsx
+++ b/output/tables/table_S3_healthy_days_2.0.xlsx
@@ -1,21 +1,362 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conireds/PM2.5_Inequalities_Chile/output/tables/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB598AC6-34CA-364F-94AD-8A67670DC732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView minimized="1" xWindow="21180" yWindow="-1360" windowWidth="17240" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="110">
+  <si>
+    <t>Municipality</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Valid days_Annual</t>
+  </si>
+  <si>
+    <t>Conforme_Annual</t>
+  </si>
+  <si>
+    <t>Chile_Annual</t>
+  </si>
+  <si>
+    <t>EPA_Annual</t>
+  </si>
+  <si>
+    <t>WHO_Annual</t>
+  </si>
+  <si>
+    <t>Valid days_Winter</t>
+  </si>
+  <si>
+    <t>Conforme_Winter</t>
+  </si>
+  <si>
+    <t>Chile_Winter</t>
+  </si>
+  <si>
+    <t>EPA_Winter</t>
+  </si>
+  <si>
+    <t>WHO_Winter</t>
+  </si>
+  <si>
+    <t>Cerrillos</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Cerro Navia</t>
+  </si>
+  <si>
+    <t>El Bosque</t>
+  </si>
+  <si>
+    <t>La Florida</t>
+  </si>
+  <si>
+    <t>Las Condes</t>
+  </si>
+  <si>
+    <t>Santiago (Parque)</t>
+  </si>
+  <si>
+    <t>Pudahuel</t>
+  </si>
+  <si>
+    <t>Puente Alto</t>
+  </si>
+  <si>
+    <t>Quilicura</t>
+  </si>
+  <si>
+    <t>Talagante</t>
+  </si>
+  <si>
+    <t>57.98</t>
+  </si>
+  <si>
+    <t>26.05</t>
+  </si>
+  <si>
+    <t>6.72</t>
+  </si>
+  <si>
+    <t>74.17</t>
+  </si>
+  <si>
+    <t>40.83</t>
+  </si>
+  <si>
+    <t>8.33</t>
+  </si>
+  <si>
+    <t>68.7</t>
+  </si>
+  <si>
+    <t>37.39</t>
+  </si>
+  <si>
+    <t>8.7</t>
+  </si>
+  <si>
+    <t>51.67</t>
+  </si>
+  <si>
+    <t>24.17</t>
+  </si>
+  <si>
+    <t>4.17</t>
+  </si>
+  <si>
+    <t>61.54</t>
+  </si>
+  <si>
+    <t>39.32</t>
+  </si>
+  <si>
+    <t>7.69</t>
+  </si>
+  <si>
+    <t>51.35</t>
+  </si>
+  <si>
+    <t>34.23</t>
+  </si>
+  <si>
+    <t>9.91</t>
+  </si>
+  <si>
+    <t>52.07</t>
+  </si>
+  <si>
+    <t>22.31</t>
+  </si>
+  <si>
+    <t>6.61</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>61.86</t>
+  </si>
+  <si>
+    <t>37.29</t>
+  </si>
+  <si>
+    <t>8.47</t>
+  </si>
+  <si>
+    <t>69.83</t>
+  </si>
+  <si>
+    <t>33.62</t>
+  </si>
+  <si>
+    <t>4.31</t>
+  </si>
+  <si>
+    <t>84.87</t>
+  </si>
+  <si>
+    <t>42.86</t>
+  </si>
+  <si>
+    <t>10.08</t>
+  </si>
+  <si>
+    <t>85.47</t>
+  </si>
+  <si>
+    <t>52.99</t>
+  </si>
+  <si>
+    <t>11.97</t>
+  </si>
+  <si>
+    <t>94.07</t>
+  </si>
+  <si>
+    <t>64.41</t>
+  </si>
+  <si>
+    <t>20.34</t>
+  </si>
+  <si>
+    <t>85.59</t>
+  </si>
+  <si>
+    <t>20.72</t>
+  </si>
+  <si>
+    <t>97.17</t>
+  </si>
+  <si>
+    <t>84.91</t>
+  </si>
+  <si>
+    <t>23.58</t>
+  </si>
+  <si>
+    <t>72.73</t>
+  </si>
+  <si>
+    <t>37.19</t>
+  </si>
+  <si>
+    <t>7.44</t>
+  </si>
+  <si>
+    <t>83.33</t>
+  </si>
+  <si>
+    <t>49.17</t>
+  </si>
+  <si>
+    <t>10.83</t>
+  </si>
+  <si>
+    <t>80.19</t>
+  </si>
+  <si>
+    <t>54.72</t>
+  </si>
+  <si>
+    <t>15.09</t>
+  </si>
+  <si>
+    <t>30.51</t>
+  </si>
+  <si>
+    <t>5.08</t>
+  </si>
+  <si>
+    <t>68.97</t>
+  </si>
+  <si>
+    <t>43.1</t>
+  </si>
+  <si>
+    <t>7.76</t>
+  </si>
+  <si>
+    <t>58.49</t>
+  </si>
+  <si>
+    <t>36.79</t>
+  </si>
+  <si>
+    <t>10.38</t>
+  </si>
+  <si>
+    <t>86.09</t>
+  </si>
+  <si>
+    <t>54.78</t>
+  </si>
+  <si>
+    <t>95.8</t>
+  </si>
+  <si>
+    <t>76.47</t>
+  </si>
+  <si>
+    <t>15.13</t>
+  </si>
+  <si>
+    <t>93.16</t>
+  </si>
+  <si>
+    <t>66.67</t>
+  </si>
+  <si>
+    <t>15.38</t>
+  </si>
+  <si>
+    <t>68.91</t>
+  </si>
+  <si>
+    <t>36.13</t>
+  </si>
+  <si>
+    <t>5.04</t>
+  </si>
+  <si>
+    <t>79.49</t>
+  </si>
+  <si>
+    <t>52.14</t>
+  </si>
+  <si>
+    <t>10.26</t>
+  </si>
+  <si>
+    <t>77.88</t>
+  </si>
+  <si>
+    <t>48.67</t>
+  </si>
+  <si>
+    <t>15.93</t>
+  </si>
+  <si>
+    <t>70.18</t>
+  </si>
+  <si>
+    <t>37.72</t>
+  </si>
+  <si>
+    <t>7.89</t>
+  </si>
+  <si>
+    <t>78.45</t>
+  </si>
+  <si>
+    <t>50.86</t>
+  </si>
+  <si>
+    <t>12.07</t>
+  </si>
+  <si>
+    <t>74.78</t>
+  </si>
+  <si>
+    <t>52.17</t>
+  </si>
+  <si>
+    <t>14.78</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -52,24 +393,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +457,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +491,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +526,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,82 +702,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Municipality</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Valid days_Annual</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Conforme_Annual</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Chile_Annual</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>EPA_Annual</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>WHO_Annual</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Valid days_Winter</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Conforme_Winter</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Chile_Winter</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>EPA_Winter</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>WHO_Winter</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
       </c>
       <c r="C2">
         <v>254</v>
@@ -439,26 +767,22 @@
       <c r="I2" t="b">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>57.98</v>
-      </c>
-      <c r="K2">
-        <v>26.05</v>
-      </c>
-      <c r="L2">
-        <v>6.72</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="J2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
       </c>
       <c r="C3">
         <v>341</v>
@@ -481,26 +805,22 @@
       <c r="I3" t="b">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>74.17</v>
-      </c>
-      <c r="K3">
-        <v>40.83</v>
-      </c>
-      <c r="L3">
-        <v>8.33</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="J3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
       </c>
       <c r="C4">
         <v>345</v>
@@ -509,13 +829,13 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>89.56999999999999</v>
+        <v>89.57</v>
       </c>
       <c r="F4">
         <v>78.55</v>
       </c>
       <c r="G4">
-        <v>40.87</v>
+        <v>40.869999999999997</v>
       </c>
       <c r="H4">
         <v>115</v>
@@ -523,26 +843,22 @@
       <c r="I4" t="b">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>68.7</v>
-      </c>
-      <c r="K4">
-        <v>37.39</v>
-      </c>
-      <c r="L4">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="J4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
       </c>
       <c r="C5">
         <v>347</v>
@@ -565,26 +881,22 @@
       <c r="I5" t="b">
         <v>1</v>
       </c>
-      <c r="J5">
-        <v>51.67</v>
-      </c>
-      <c r="K5">
-        <v>24.17</v>
-      </c>
-      <c r="L5">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="J5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
       </c>
       <c r="C6">
         <v>332</v>
@@ -593,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>85.23999999999999</v>
+        <v>85.24</v>
       </c>
       <c r="F6">
         <v>74.7</v>
@@ -607,26 +919,22 @@
       <c r="I6" t="b">
         <v>1</v>
       </c>
-      <c r="J6">
-        <v>61.54</v>
-      </c>
-      <c r="K6">
-        <v>39.32</v>
-      </c>
-      <c r="L6">
-        <v>7.69</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="J6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
       </c>
       <c r="C7">
         <v>338</v>
@@ -649,26 +957,22 @@
       <c r="I7" t="b">
         <v>1</v>
       </c>
-      <c r="J7">
-        <v>51.35</v>
-      </c>
-      <c r="K7">
-        <v>34.23</v>
-      </c>
-      <c r="L7">
-        <v>9.91</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="J7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
       </c>
       <c r="C8">
         <v>349</v>
@@ -691,26 +995,22 @@
       <c r="I8" t="b">
         <v>1</v>
       </c>
-      <c r="J8">
-        <v>52.07</v>
-      </c>
-      <c r="K8">
-        <v>22.31</v>
-      </c>
-      <c r="L8">
-        <v>6.61</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="J8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
       </c>
       <c r="C9">
         <v>319</v>
@@ -719,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>87.15000000000001</v>
+        <v>87.15</v>
       </c>
       <c r="F9">
         <v>73.67</v>
@@ -733,26 +1033,22 @@
       <c r="I9" t="b">
         <v>1</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>70</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>40</v>
       </c>
-      <c r="L9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="L9" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
       </c>
       <c r="C10">
         <v>336</v>
@@ -764,7 +1060,7 @@
         <v>86.61</v>
       </c>
       <c r="F10">
-        <v>76.79000000000001</v>
+        <v>76.790000000000006</v>
       </c>
       <c r="G10">
         <v>30.95</v>
@@ -775,26 +1071,22 @@
       <c r="I10" t="b">
         <v>1</v>
       </c>
-      <c r="J10">
-        <v>61.86</v>
-      </c>
-      <c r="K10">
-        <v>37.29</v>
-      </c>
-      <c r="L10">
-        <v>8.470000000000001</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="J10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
       </c>
       <c r="C11">
         <v>329</v>
@@ -817,26 +1109,22 @@
       <c r="I11" t="b">
         <v>1</v>
       </c>
-      <c r="J11">
-        <v>69.83</v>
-      </c>
-      <c r="K11">
-        <v>33.62</v>
-      </c>
-      <c r="L11">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="J11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
       </c>
       <c r="C12">
         <v>344</v>
@@ -859,26 +1147,22 @@
       <c r="I12" t="b">
         <v>1</v>
       </c>
-      <c r="J12">
-        <v>84.87</v>
-      </c>
-      <c r="K12">
-        <v>42.86</v>
-      </c>
-      <c r="L12">
-        <v>10.08</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="J12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
       </c>
       <c r="C13">
         <v>339</v>
@@ -887,13 +1171,13 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>94.98999999999999</v>
+        <v>94.99</v>
       </c>
       <c r="F13">
         <v>83.48</v>
       </c>
       <c r="G13">
-        <v>38.05</v>
+        <v>38.049999999999997</v>
       </c>
       <c r="H13">
         <v>117</v>
@@ -901,26 +1185,22 @@
       <c r="I13" t="b">
         <v>1</v>
       </c>
-      <c r="J13">
-        <v>85.47</v>
-      </c>
-      <c r="K13">
-        <v>52.99</v>
-      </c>
-      <c r="L13">
-        <v>11.97</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="J13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
       </c>
       <c r="C14">
         <v>341</v>
@@ -932,7 +1212,7 @@
         <v>97.95</v>
       </c>
       <c r="F14">
-        <v>87.68000000000001</v>
+        <v>87.68</v>
       </c>
       <c r="G14">
         <v>49.56</v>
@@ -943,26 +1223,22 @@
       <c r="I14" t="b">
         <v>1</v>
       </c>
-      <c r="J14">
-        <v>94.06999999999999</v>
-      </c>
-      <c r="K14">
-        <v>64.41</v>
-      </c>
-      <c r="L14">
-        <v>20.34</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="J14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
       </c>
       <c r="C15">
         <v>328</v>
@@ -985,26 +1261,22 @@
       <c r="I15" t="b">
         <v>1</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>100</v>
       </c>
-      <c r="K15">
-        <v>85.59</v>
-      </c>
-      <c r="L15">
-        <v>20.72</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="K15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
       </c>
       <c r="C16">
         <v>337</v>
@@ -1016,7 +1288,7 @@
         <v>99.11</v>
       </c>
       <c r="F16">
-        <v>94.95999999999999</v>
+        <v>94.96</v>
       </c>
       <c r="G16">
         <v>49.55</v>
@@ -1027,26 +1299,22 @@
       <c r="I16" t="b">
         <v>1</v>
       </c>
-      <c r="J16">
-        <v>97.17</v>
-      </c>
-      <c r="K16">
-        <v>84.91</v>
-      </c>
-      <c r="L16">
-        <v>23.58</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Santiago (Parque)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="J16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
       </c>
       <c r="C17">
         <v>352</v>
@@ -1069,26 +1337,22 @@
       <c r="I17" t="b">
         <v>1</v>
       </c>
-      <c r="J17">
-        <v>72.73</v>
-      </c>
-      <c r="K17">
-        <v>37.19</v>
-      </c>
-      <c r="L17">
-        <v>7.44</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Santiago (Parque)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="J17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
       </c>
       <c r="C18">
         <v>343</v>
@@ -1100,10 +1364,10 @@
         <v>93</v>
       </c>
       <c r="F18">
-        <v>79.01000000000001</v>
+        <v>79.010000000000005</v>
       </c>
       <c r="G18">
-        <v>40.23</v>
+        <v>40.229999999999997</v>
       </c>
       <c r="H18">
         <v>120</v>
@@ -1111,26 +1375,22 @@
       <c r="I18" t="b">
         <v>1</v>
       </c>
-      <c r="J18">
-        <v>83.33</v>
-      </c>
-      <c r="K18">
-        <v>49.17</v>
-      </c>
-      <c r="L18">
-        <v>10.83</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Santiago (Parque)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="J18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
       </c>
       <c r="C19">
         <v>335</v>
@@ -1153,26 +1413,22 @@
       <c r="I19" t="b">
         <v>1</v>
       </c>
-      <c r="J19">
-        <v>80.19</v>
-      </c>
-      <c r="K19">
-        <v>54.72</v>
-      </c>
-      <c r="L19">
-        <v>15.09</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="J19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
       </c>
       <c r="C20">
         <v>348</v>
@@ -1184,7 +1440,7 @@
         <v>86.78</v>
       </c>
       <c r="F20">
-        <v>73.84999999999999</v>
+        <v>73.849999999999994</v>
       </c>
       <c r="G20">
         <v>47.41</v>
@@ -1195,26 +1451,22 @@
       <c r="I20" t="b">
         <v>1</v>
       </c>
-      <c r="J20">
-        <v>64.41</v>
-      </c>
-      <c r="K20">
-        <v>30.51</v>
-      </c>
-      <c r="L20">
-        <v>5.08</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="J20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
       </c>
       <c r="C21">
         <v>325</v>
@@ -1237,26 +1489,22 @@
       <c r="I21" t="b">
         <v>1</v>
       </c>
-      <c r="J21">
-        <v>68.97</v>
-      </c>
-      <c r="K21">
-        <v>43.1</v>
-      </c>
-      <c r="L21">
-        <v>7.76</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="J21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
       </c>
       <c r="C22">
         <v>329</v>
@@ -1279,26 +1527,22 @@
       <c r="I22" t="b">
         <v>1</v>
       </c>
-      <c r="J22">
-        <v>58.49</v>
-      </c>
-      <c r="K22">
-        <v>36.79</v>
-      </c>
-      <c r="L22">
-        <v>10.38</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="J22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
       </c>
       <c r="C23">
         <v>344</v>
@@ -1307,7 +1551,7 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>95.34999999999999</v>
+        <v>95.35</v>
       </c>
       <c r="F23">
         <v>83.72</v>
@@ -1321,26 +1565,22 @@
       <c r="I23" t="b">
         <v>1</v>
       </c>
-      <c r="J23">
-        <v>86.09</v>
-      </c>
-      <c r="K23">
-        <v>54.78</v>
-      </c>
-      <c r="L23">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="J23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
       </c>
       <c r="C24">
         <v>308</v>
@@ -1352,7 +1592,7 @@
         <v>97.08</v>
       </c>
       <c r="F24">
-        <v>87.01000000000001</v>
+        <v>87.01</v>
       </c>
       <c r="G24">
         <v>38.31</v>
@@ -1363,26 +1603,22 @@
       <c r="I24" t="b">
         <v>1</v>
       </c>
-      <c r="J24">
-        <v>95.8</v>
-      </c>
-      <c r="K24">
-        <v>76.47</v>
-      </c>
-      <c r="L24">
-        <v>15.13</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="J24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
       </c>
       <c r="C25">
         <v>348</v>
@@ -1394,7 +1630,7 @@
         <v>97.7</v>
       </c>
       <c r="F25">
-        <v>88.79000000000001</v>
+        <v>88.79</v>
       </c>
       <c r="G25">
         <v>43.39</v>
@@ -1405,26 +1641,22 @@
       <c r="I25" t="b">
         <v>1</v>
       </c>
-      <c r="J25">
-        <v>93.16</v>
-      </c>
-      <c r="K25">
-        <v>66.67</v>
-      </c>
-      <c r="L25">
-        <v>15.38</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="J25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
       </c>
       <c r="C26">
         <v>337</v>
@@ -1447,26 +1679,22 @@
       <c r="I26" t="b">
         <v>1</v>
       </c>
-      <c r="J26">
-        <v>68.91</v>
-      </c>
-      <c r="K26">
-        <v>36.13</v>
-      </c>
-      <c r="L26">
-        <v>5.04</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="J26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
       </c>
       <c r="C27">
         <v>348</v>
@@ -1489,26 +1717,22 @@
       <c r="I27" t="b">
         <v>1</v>
       </c>
-      <c r="J27">
-        <v>79.48999999999999</v>
-      </c>
-      <c r="K27">
-        <v>52.14</v>
-      </c>
-      <c r="L27">
-        <v>10.26</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="J27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
       </c>
       <c r="C28">
         <v>337</v>
@@ -1520,7 +1744,7 @@
         <v>92.58</v>
       </c>
       <c r="F28">
-        <v>82.79000000000001</v>
+        <v>82.79</v>
       </c>
       <c r="G28">
         <v>50.74</v>
@@ -1531,26 +1755,22 @@
       <c r="I28" t="b">
         <v>1</v>
       </c>
-      <c r="J28">
-        <v>77.88</v>
-      </c>
-      <c r="K28">
-        <v>48.67</v>
-      </c>
-      <c r="L28">
-        <v>15.93</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="J28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
       </c>
       <c r="C29">
         <v>336</v>
@@ -1562,7 +1782,7 @@
         <v>89.58</v>
       </c>
       <c r="F29">
-        <v>77.68000000000001</v>
+        <v>77.680000000000007</v>
       </c>
       <c r="G29">
         <v>44.94</v>
@@ -1573,26 +1793,22 @@
       <c r="I29" t="b">
         <v>1</v>
       </c>
-      <c r="J29">
-        <v>70.18000000000001</v>
-      </c>
-      <c r="K29">
-        <v>37.72</v>
-      </c>
-      <c r="L29">
-        <v>7.89</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="J29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
       </c>
       <c r="C30">
         <v>332</v>
@@ -1615,26 +1831,22 @@
       <c r="I30" t="b">
         <v>1</v>
       </c>
-      <c r="J30">
-        <v>78.45</v>
-      </c>
-      <c r="K30">
-        <v>50.86</v>
-      </c>
-      <c r="L30">
-        <v>12.07</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="J30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>15</v>
       </c>
       <c r="C31">
         <v>338</v>
@@ -1657,17 +1869,18 @@
       <c r="I31" t="b">
         <v>1</v>
       </c>
-      <c r="J31">
-        <v>74.78</v>
-      </c>
-      <c r="K31">
-        <v>52.17</v>
-      </c>
-      <c r="L31">
-        <v>14.78</v>
+      <c r="J31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>